--- a/Check.xlsx
+++ b/Check.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="W:\Обучение Макс\Diplom\fmh_android_updated\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B94AB7D-14BB-422C-964E-065CF0D727CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B249208-B723-40E3-9619-7EF4A1C8D21E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="945" yWindow="465" windowWidth="27615" windowHeight="15015" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Чек-лист" sheetId="1" r:id="rId1"/>
@@ -20,14 +20,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="599" uniqueCount="249">
   <si>
     <t>Чек-лист тестирования</t>
   </si>
   <si>
-    <t>Приложение «Мобильный хоспис» · Android API 36 · статусы заполняются во время ручного прогона</t>
-  </si>
-  <si>
     <t>ID</t>
   </si>
   <si>
@@ -139,9 +136,6 @@
     <t>AUTH-06</t>
   </si>
   <si>
-    <t>Неверные учётные данные вызывают сообщение "Login or password cannot be empty"</t>
-  </si>
-  <si>
     <t>AUTH-07</t>
   </si>
   <si>
@@ -163,9 +157,6 @@
     <t>При отсутствии сети отображается сообщение о сетевом подключении</t>
   </si>
   <si>
-    <t>Ручное управление сетью</t>
-  </si>
-  <si>
     <t>MAIN-01</t>
   </si>
   <si>
@@ -304,9 +295,6 @@
     <t>Ошибка загрузки сопровождается сообщением и кнопкой OK</t>
   </si>
   <si>
-    <t>Нужно отключение сети или подмена ответа</t>
-  </si>
-  <si>
     <t>NEWS-09</t>
   </si>
   <si>
@@ -604,9 +592,6 @@
     <t>Не пройден</t>
   </si>
   <si>
-    <t>BUG-002. Фактически: на Main отображаются новости за 30.09, хотя в полном списке есть более свежие новости. Дата устройства установлена корректно.</t>
-  </si>
-  <si>
     <t>CTRL-08</t>
   </si>
   <si>
@@ -617,13 +602,178 @@
   </si>
   <si>
     <t>BUG-001. Фактически: в поле Creation date отображается некорректная последовательность чисел и точек вместо читаемой даты и времени публикации.</t>
+  </si>
+  <si>
+    <t>NF-01</t>
+  </si>
+  <si>
+    <t>Шрифт</t>
+  </si>
+  <si>
+    <t>При максимальном системном шрифте на авторизации поля и кнопка входа читаемы и доступны</t>
+  </si>
+  <si>
+    <t>Удобство</t>
+  </si>
+  <si>
+    <t>NF-02</t>
+  </si>
+  <si>
+    <t>При максимальном системном шрифте список и раскрытая карточка новости читаемы; кнопки доступны</t>
+  </si>
+  <si>
+    <t>NF-03</t>
+  </si>
+  <si>
+    <t>При максимальном системном шрифте форма создания новости позволяет заполнить поля и нажать сохранение</t>
+  </si>
+  <si>
+    <t>NF-04</t>
+  </si>
+  <si>
+    <t>Сворачивание</t>
+  </si>
+  <si>
+    <t>После сворачивания и возврата со списка новостей приложение не падает и остаётся на экране News</t>
+  </si>
+  <si>
+    <t>Устойчивость</t>
+  </si>
+  <si>
+    <t>NF-05</t>
+  </si>
+  <si>
+    <t>NF-06</t>
+  </si>
+  <si>
+    <t>NF-07</t>
+  </si>
+  <si>
+    <t>Восстановление сети</t>
+  </si>
+  <si>
+    <t>После ошибки входа без сети восстановление связи позволяет войти повторной попыткой без перезапуска приложения</t>
+  </si>
+  <si>
+    <t>Восстановление</t>
+  </si>
+  <si>
+    <t>NF-08</t>
+  </si>
+  <si>
+    <t>После ошибки загрузки без сети восстановление связи позволяет обновить новости без перезапуска приложения</t>
+  </si>
+  <si>
+    <t>NF-09</t>
+  </si>
+  <si>
+    <t>Поворот экрана</t>
+  </si>
+  <si>
+    <t>После поворота в горизонтальную ориентацию и обратно авторизация отображается без перекрытия полей и кнопки</t>
+  </si>
+  <si>
+    <t>Адаптация UI</t>
+  </si>
+  <si>
+    <t>NF-10</t>
+  </si>
+  <si>
+    <t>После поворота в горизонтальную ориентацию и обратно список новостей читаем и доступен для взаимодействия</t>
+  </si>
+  <si>
+    <t>NF-11</t>
+  </si>
+  <si>
+    <t>После поворота заполненной формы новости и возврата поля доступны, заголовок и описание сохранены</t>
+  </si>
+  <si>
+    <t>NF-12</t>
+  </si>
+  <si>
+    <t>Маскировка пароля</t>
+  </si>
+  <si>
+    <t>После ввода тестового пароля и ухода из поля его полное значение не отображается открытым текстом</t>
+  </si>
+  <si>
+    <t>Безопасность UI</t>
+  </si>
+  <si>
+    <t>NF-13</t>
+  </si>
+  <si>
+    <t>Локализация RU</t>
+  </si>
+  <si>
+    <t>При русском языке подписи и сообщение о пустых полях авторизации отображаются по-русски без обрезания текста</t>
+  </si>
+  <si>
+    <t>Локализация</t>
+  </si>
+  <si>
+    <t>NF-14</t>
+  </si>
+  <si>
+    <t>При русском языке интерфейс списка новостей и фильтра переведён, текст читается и помещается</t>
+  </si>
+  <si>
+    <t>NF-15</t>
+  </si>
+  <si>
+    <t>При русском языке форма новости, предупреждение о выходе и сообщение о пустых полях переведены и читаемы</t>
+  </si>
+  <si>
+    <t>NF-16</t>
+  </si>
+  <si>
+    <t>Локализация EN</t>
+  </si>
+  <si>
+    <t>При английском языке подписи и сообщение о пустых полях авторизации отображаются по-английски без обрезания текста</t>
+  </si>
+  <si>
+    <t>NF-17</t>
+  </si>
+  <si>
+    <t>При английском языке интерфейс списка новостей и фильтра переведён, текст читается и помещается</t>
+  </si>
+  <si>
+    <t>NF-18</t>
+  </si>
+  <si>
+    <t>При английском языке форма новости, предупреждение о выходе и сообщение о пустых полях переведены и читаемы</t>
+  </si>
+  <si>
+    <t>Приложение «Мобильный хоспис»</t>
+  </si>
+  <si>
+    <t>Нефункциональные проверки</t>
+  </si>
+  <si>
+    <t>После сворачивания во время загрузки приложения и возврата загрузка завершается без зависшего индикатора</t>
+  </si>
+  <si>
+    <t>После сворачивания и возврата в форму создания новости введённые заголовок и описание сохраняются</t>
+  </si>
+  <si>
+    <t>BUG-004. ФР: Текст в полях логин и пароль не помещается в поле</t>
+  </si>
+  <si>
+    <t>Неверные учётные данные вызывают сообщение "Wrong login or password"; пользователь остаётся на авторизации</t>
+  </si>
+  <si>
+    <t>BUG-003. Фактически: Something went wrong. Try again later. Подтверждено TC-AUTH-005 в автопрогоне 22.10.2026.</t>
+  </si>
+  <si>
+    <t>BUG-002. Сначала на Main были новости за 30.09 при наличии более свежих. Повторно не воспроизводится (со слов Игоря). Причина неизвестна. Статус — первый прогон.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -661,8 +811,19 @@
       <sz val="11"/>
       <name val="Carlito"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF795500"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -672,6 +833,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF244A62"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -757,7 +928,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -798,30 +969,73 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="12">
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF795500"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF7F6000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -836,10 +1050,32 @@
     <dxf>
       <font>
         <b/>
+        <color rgb="FF375623"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF795500"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
         <color rgb="FF7F6000"/>
       </font>
       <fill>
-        <patternFill>
+        <patternFill patternType="solid">
           <bgColor rgb="FFFFF2CC"/>
         </patternFill>
       </fill>
@@ -850,7 +1086,7 @@
         <color rgb="FFC00000"/>
       </font>
       <fill>
-        <patternFill>
+        <patternFill patternType="solid">
           <bgColor rgb="FFFCE4D6"/>
         </patternFill>
       </fill>
@@ -861,7 +1097,51 @@
         <color rgb="FF375623"/>
       </font>
       <fill>
-        <patternFill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF795500"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF7F6000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF375623"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
           <bgColor rgb="FFE2F0D9"/>
         </patternFill>
       </fill>
@@ -877,30 +1157,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ns1:Ignorable="xr xr3" id="1" ns2:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="CheckListTable" displayName="CheckListTable" ref="A5:G83" totalsRowShown="0">
-  <x:autoFilter ref="A5:G83" ns2:uid="{00000000-0009-0000-0100-000001000000}">
-    <x:filterColumn colId="0" hiddenButton="1" showButton="0"/>
-    <x:filterColumn colId="1" hiddenButton="1" showButton="0"/>
-    <x:filterColumn colId="2" hiddenButton="1" showButton="0"/>
-    <x:filterColumn colId="3" hiddenButton="1" showButton="0"/>
-    <x:filterColumn colId="4" hiddenButton="1" showButton="0"/>
-    <x:filterColumn colId="5" hiddenButton="0" showButton="1"/>
-    <x:filterColumn colId="6" hiddenButton="1" showButton="0"/>
-  </x:autoFilter>
-  <x:tableColumns count="7">
-    <x:tableColumn id="1" ns3:uid="{00000000-0010-0000-0000-000001000000}" name="ID"/>
-    <x:tableColumn id="2" ns3:uid="{00000000-0010-0000-0000-000002000000}" name="Раздел"/>
-    <x:tableColumn id="3" ns3:uid="{00000000-0010-0000-0000-000003000000}" name="Проверка"/>
-    <x:tableColumn id="4" ns3:uid="{00000000-0010-0000-0000-000004000000}" name="Вид"/>
-    <x:tableColumn id="5" ns3:uid="{00000000-0010-0000-0000-000005000000}" name="Приоритет"/>
-    <x:tableColumn id="7" ns3:uid="{00000000-0010-0000-0000-000007000000}" name="Статус"/>
-    <x:tableColumn id="8" ns3:uid="{00000000-0010-0000-0000-000008000000}" name="Комментарий"/>
-  </x:tableColumns>
-  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</x:table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1098,7 +1354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G83"/>
+  <dimension ref="A1:G103"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1132,7 +1388,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>1</v>
+        <v>241</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -1152,1694 +1408,2140 @@
     </row>
     <row r="5" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="C5" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="D5" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="E5" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="F5" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="G5" s="7" t="s">
         <v>7</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="C6" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="D6" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="8" t="s">
-        <v>12</v>
-      </c>
       <c r="E6" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" s="14" t="s">
-        <v>14</v>
+        <v>12</v>
+      </c>
+      <c r="F6" s="25" t="s">
+        <v>13</v>
       </c>
       <c r="G6" s="8"/>
     </row>
     <row r="7" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="9" t="s">
+      <c r="D7" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="9" t="s">
-        <v>17</v>
-      </c>
       <c r="E7" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7" s="15" t="s">
-        <v>14</v>
+        <v>12</v>
+      </c>
+      <c r="F7" s="25" t="s">
+        <v>13</v>
       </c>
       <c r="G7" s="9"/>
     </row>
     <row r="8" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="9" t="s">
+      <c r="D8" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="9" t="s">
-        <v>20</v>
-      </c>
       <c r="E8" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F8" s="15" t="s">
-        <v>14</v>
+        <v>12</v>
+      </c>
+      <c r="F8" s="25" t="s">
+        <v>13</v>
       </c>
       <c r="G8" s="9"/>
     </row>
     <row r="9" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>22</v>
-      </c>
       <c r="D9" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="F9" s="15" t="s">
-        <v>14</v>
+        <v>22</v>
+      </c>
+      <c r="F9" s="25" t="s">
+        <v>13</v>
       </c>
       <c r="G9" s="9"/>
     </row>
     <row r="10" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="C10" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="D10" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D10" s="9" t="s">
-        <v>27</v>
-      </c>
       <c r="E10" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F10" s="15" t="s">
-        <v>14</v>
+        <v>12</v>
+      </c>
+      <c r="F10" s="25" t="s">
+        <v>13</v>
       </c>
       <c r="G10" s="9"/>
     </row>
     <row r="11" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" s="9" t="s">
+      <c r="D11" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="D11" s="9" t="s">
-        <v>30</v>
-      </c>
       <c r="E11" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11" s="15" t="s">
-        <v>14</v>
+        <v>12</v>
+      </c>
+      <c r="F11" s="25" t="s">
+        <v>13</v>
       </c>
       <c r="G11" s="9"/>
     </row>
     <row r="12" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="B12" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C12" s="9" t="s">
+      <c r="D12" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="9" t="s">
-        <v>33</v>
-      </c>
       <c r="E12" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F12" s="15" t="s">
-        <v>14</v>
+        <v>12</v>
+      </c>
+      <c r="F12" s="25" t="s">
+        <v>13</v>
       </c>
       <c r="G12" s="9"/>
     </row>
     <row r="13" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>35</v>
-      </c>
       <c r="D13" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F13" s="15" t="s">
-        <v>14</v>
+        <v>12</v>
+      </c>
+      <c r="F13" s="25" t="s">
+        <v>13</v>
       </c>
       <c r="G13" s="9"/>
     </row>
     <row r="14" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="B14" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>37</v>
-      </c>
       <c r="D14" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F14" s="15" t="s">
-        <v>14</v>
+        <v>12</v>
+      </c>
+      <c r="F14" s="25" t="s">
+        <v>13</v>
       </c>
       <c r="G14" s="9"/>
     </row>
     <row r="15" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>39</v>
+        <v>246</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F15" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="G15" s="9"/>
+        <v>12</v>
+      </c>
+      <c r="F15" s="25" t="s">
+        <v>189</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>247</v>
+      </c>
     </row>
     <row r="16" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>42</v>
-      </c>
       <c r="E16" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="F16" s="15" t="s">
-        <v>14</v>
+        <v>22</v>
+      </c>
+      <c r="F16" s="25" t="s">
+        <v>13</v>
       </c>
       <c r="G16" s="9"/>
     </row>
     <row r="17" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="F17" s="15" t="s">
-        <v>14</v>
+        <v>22</v>
+      </c>
+      <c r="F17" s="25" t="s">
+        <v>13</v>
       </c>
       <c r="G17" s="9"/>
     </row>
     <row r="18" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F18" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="G18" s="9" t="s">
-        <v>47</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="F18" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="G18" s="9"/>
     </row>
     <row r="19" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="F19" s="15" t="s">
-        <v>14</v>
+        <v>22</v>
+      </c>
+      <c r="F19" s="25" t="s">
+        <v>13</v>
       </c>
       <c r="G19" s="9"/>
     </row>
     <row r="20" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B20" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C20" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="C20" s="9" t="s">
-        <v>52</v>
-      </c>
       <c r="D20" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F20" s="15" t="s">
-        <v>14</v>
+        <v>12</v>
+      </c>
+      <c r="F20" s="25" t="s">
+        <v>13</v>
       </c>
       <c r="G20" s="9"/>
     </row>
     <row r="21" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="F21" s="15" t="s">
-        <v>14</v>
+        <v>22</v>
+      </c>
+      <c r="F21" s="25" t="s">
+        <v>13</v>
       </c>
       <c r="G21" s="9"/>
     </row>
     <row r="22" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="F22" s="15" t="s">
-        <v>14</v>
+        <v>22</v>
+      </c>
+      <c r="F22" s="25" t="s">
+        <v>13</v>
       </c>
       <c r="G22" s="9"/>
     </row>
     <row r="23" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="F23" s="15" t="s">
-        <v>14</v>
+        <v>56</v>
+      </c>
+      <c r="F23" s="25" t="s">
+        <v>13</v>
       </c>
       <c r="G23" s="9"/>
     </row>
     <row r="24" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F24" s="15" t="s">
-        <v>14</v>
+        <v>12</v>
+      </c>
+      <c r="F24" s="25" t="s">
+        <v>13</v>
       </c>
       <c r="G24" s="9"/>
     </row>
     <row r="25" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F25" s="15" t="s">
-        <v>14</v>
+        <v>12</v>
+      </c>
+      <c r="F25" s="25" t="s">
+        <v>13</v>
       </c>
       <c r="G25" s="9"/>
     </row>
     <row r="26" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="F26" s="15" t="s">
-        <v>14</v>
+        <v>56</v>
+      </c>
+      <c r="F26" s="25" t="s">
+        <v>13</v>
       </c>
       <c r="G26" s="9"/>
     </row>
     <row r="27" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="12" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F27" s="15" t="s">
-        <v>14</v>
+        <v>12</v>
+      </c>
+      <c r="F27" s="25" t="s">
+        <v>13</v>
       </c>
       <c r="G27" s="9"/>
     </row>
     <row r="28" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="F28" s="15" t="s">
-        <v>14</v>
+        <v>56</v>
+      </c>
+      <c r="F28" s="25" t="s">
+        <v>13</v>
       </c>
       <c r="G28" s="9"/>
     </row>
     <row r="29" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="F29" s="15" t="s">
-        <v>14</v>
+        <v>22</v>
+      </c>
+      <c r="F29" s="25" t="s">
+        <v>13</v>
       </c>
       <c r="G29" s="9"/>
     </row>
     <row r="30" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="12" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="F30" s="15" t="s">
-        <v>14</v>
+        <v>22</v>
+      </c>
+      <c r="F30" s="25" t="s">
+        <v>13</v>
       </c>
       <c r="G30" s="9"/>
     </row>
     <row r="31" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F31" s="15" t="s">
-        <v>14</v>
+        <v>12</v>
+      </c>
+      <c r="F31" s="25" t="s">
+        <v>13</v>
       </c>
       <c r="G31" s="9"/>
     </row>
     <row r="32" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="12" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B32" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C32" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="C32" s="9" t="s">
-        <v>79</v>
-      </c>
       <c r="D32" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="F32" s="15" t="s">
-        <v>14</v>
+        <v>22</v>
+      </c>
+      <c r="F32" s="25" t="s">
+        <v>13</v>
       </c>
       <c r="G32" s="9"/>
     </row>
     <row r="33" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="12" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="F33" s="15" t="s">
-        <v>14</v>
+        <v>22</v>
+      </c>
+      <c r="F33" s="25" t="s">
+        <v>13</v>
       </c>
       <c r="G33" s="9"/>
     </row>
     <row r="34" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="12" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="F34" s="15" t="s">
-        <v>14</v>
+        <v>22</v>
+      </c>
+      <c r="F34" s="25" t="s">
+        <v>13</v>
       </c>
       <c r="G34" s="9"/>
     </row>
     <row r="35" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="12" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="F35" s="15" t="s">
-        <v>14</v>
+        <v>22</v>
+      </c>
+      <c r="F35" s="25" t="s">
+        <v>13</v>
       </c>
       <c r="G35" s="9"/>
     </row>
     <row r="36" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="B36" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E36" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F36" s="25" t="s">
+        <v>85</v>
+      </c>
+      <c r="G36" s="9" t="s">
         <v>86</v>
-      </c>
-      <c r="B36" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="C36" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="D36" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="E36" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="F36" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="G36" s="9" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="F37" s="15" t="s">
-        <v>14</v>
+        <v>56</v>
+      </c>
+      <c r="F37" s="25" t="s">
+        <v>13</v>
       </c>
       <c r="G37" s="9"/>
     </row>
     <row r="38" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="12" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="F38" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="G38" s="9" t="s">
-        <v>94</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="F38" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="G38" s="9"/>
     </row>
     <row r="39" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="12" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F39" s="15" t="s">
-        <v>14</v>
+        <v>12</v>
+      </c>
+      <c r="F39" s="25" t="s">
+        <v>13</v>
       </c>
       <c r="G39" s="9"/>
     </row>
     <row r="40" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="12" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F40" s="15" t="s">
-        <v>88</v>
+        <v>12</v>
+      </c>
+      <c r="F40" s="25" t="s">
+        <v>85</v>
       </c>
       <c r="G40" s="9" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="12" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="F41" s="15" t="s">
-        <v>14</v>
+        <v>22</v>
+      </c>
+      <c r="F41" s="25" t="s">
+        <v>13</v>
       </c>
       <c r="G41" s="9"/>
     </row>
     <row r="42" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="12" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="F42" s="15" t="s">
-        <v>14</v>
+        <v>22</v>
+      </c>
+      <c r="F42" s="25" t="s">
+        <v>13</v>
       </c>
       <c r="G42" s="9"/>
     </row>
     <row r="43" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="12" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F43" s="15" t="s">
-        <v>14</v>
+        <v>12</v>
+      </c>
+      <c r="F43" s="25" t="s">
+        <v>13</v>
       </c>
       <c r="G43" s="9"/>
     </row>
     <row r="44" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="12" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F44" s="15" t="s">
-        <v>14</v>
+        <v>12</v>
+      </c>
+      <c r="F44" s="25" t="s">
+        <v>13</v>
       </c>
       <c r="G44" s="9"/>
     </row>
     <row r="45" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="12" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="F45" s="15" t="s">
-        <v>14</v>
+        <v>22</v>
+      </c>
+      <c r="F45" s="25" t="s">
+        <v>13</v>
       </c>
       <c r="G45" s="9"/>
     </row>
     <row r="46" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="12" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F46" s="15" t="s">
-        <v>14</v>
+        <v>12</v>
+      </c>
+      <c r="F46" s="25" t="s">
+        <v>13</v>
       </c>
       <c r="G46" s="9"/>
     </row>
     <row r="47" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="12" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="F47" s="15" t="s">
-        <v>14</v>
+        <v>22</v>
+      </c>
+      <c r="F47" s="25" t="s">
+        <v>13</v>
       </c>
       <c r="G47" s="9"/>
     </row>
     <row r="48" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="12" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E48" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="F48" s="15" t="s">
-        <v>14</v>
+        <v>56</v>
+      </c>
+      <c r="F48" s="25" t="s">
+        <v>13</v>
       </c>
       <c r="G48" s="9"/>
     </row>
     <row r="49" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="12" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F49" s="15" t="s">
-        <v>14</v>
+        <v>12</v>
+      </c>
+      <c r="F49" s="25" t="s">
+        <v>13</v>
       </c>
       <c r="G49" s="9"/>
     </row>
     <row r="50" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="12" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E50" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="F50" s="15" t="s">
-        <v>14</v>
+        <v>22</v>
+      </c>
+      <c r="F50" s="25" t="s">
+        <v>13</v>
       </c>
       <c r="G50" s="9"/>
     </row>
     <row r="51" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="12" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="F51" s="15" t="s">
-        <v>14</v>
+        <v>22</v>
+      </c>
+      <c r="F51" s="25" t="s">
+        <v>13</v>
       </c>
       <c r="G51" s="9"/>
     </row>
     <row r="52" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="12" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E52" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="F52" s="15" t="s">
-        <v>14</v>
+        <v>22</v>
+      </c>
+      <c r="F52" s="25" t="s">
+        <v>13</v>
       </c>
       <c r="G52" s="9"/>
     </row>
     <row r="53" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="12" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="F53" s="15" t="s">
-        <v>14</v>
+        <v>22</v>
+      </c>
+      <c r="F53" s="25" t="s">
+        <v>13</v>
       </c>
       <c r="G53" s="9"/>
     </row>
     <row r="54" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="12" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E54" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="F54" s="15" t="s">
-        <v>14</v>
+        <v>22</v>
+      </c>
+      <c r="F54" s="25" t="s">
+        <v>13</v>
       </c>
       <c r="G54" s="9"/>
     </row>
     <row r="55" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="12" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F55" s="15" t="s">
-        <v>14</v>
+        <v>12</v>
+      </c>
+      <c r="F55" s="25" t="s">
+        <v>13</v>
       </c>
       <c r="G55" s="9"/>
     </row>
     <row r="56" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="12" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E56" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F56" s="15" t="s">
-        <v>14</v>
+        <v>12</v>
+      </c>
+      <c r="F56" s="25" t="s">
+        <v>13</v>
       </c>
       <c r="G56" s="9"/>
     </row>
     <row r="57" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="12" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="D57" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="F57" s="15" t="s">
-        <v>14</v>
+        <v>22</v>
+      </c>
+      <c r="F57" s="25" t="s">
+        <v>13</v>
       </c>
       <c r="G57" s="9"/>
     </row>
     <row r="58" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="12" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D58" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E58" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="F58" s="15" t="s">
-        <v>14</v>
+        <v>22</v>
+      </c>
+      <c r="F58" s="25" t="s">
+        <v>13</v>
       </c>
       <c r="G58" s="9"/>
     </row>
     <row r="59" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="12" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="D59" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="F59" s="15" t="s">
-        <v>14</v>
+        <v>56</v>
+      </c>
+      <c r="F59" s="25" t="s">
+        <v>13</v>
       </c>
       <c r="G59" s="9"/>
     </row>
     <row r="60" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="12" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E60" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F60" s="15" t="s">
-        <v>14</v>
+        <v>12</v>
+      </c>
+      <c r="F60" s="25" t="s">
+        <v>13</v>
       </c>
       <c r="G60" s="9"/>
     </row>
     <row r="61" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="12" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="D61" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="F61" s="15" t="s">
-        <v>14</v>
+        <v>22</v>
+      </c>
+      <c r="F61" s="25" t="s">
+        <v>13</v>
       </c>
       <c r="G61" s="9"/>
     </row>
     <row r="62" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="12" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C62" s="9" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="D62" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E62" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F62" s="15" t="s">
-        <v>14</v>
+        <v>12</v>
+      </c>
+      <c r="F62" s="25" t="s">
+        <v>13</v>
       </c>
       <c r="G62" s="9"/>
     </row>
     <row r="63" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="12" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C63" s="9" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D63" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F63" s="15" t="s">
-        <v>14</v>
+        <v>12</v>
+      </c>
+      <c r="F63" s="25" t="s">
+        <v>13</v>
       </c>
       <c r="G63" s="9"/>
     </row>
     <row r="64" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="12" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C64" s="9" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="D64" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E64" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="F64" s="15" t="s">
-        <v>14</v>
+        <v>22</v>
+      </c>
+      <c r="F64" s="25" t="s">
+        <v>13</v>
       </c>
       <c r="G64" s="9"/>
     </row>
     <row r="65" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="12" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="D65" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="F65" s="15" t="s">
-        <v>14</v>
+        <v>22</v>
+      </c>
+      <c r="F65" s="25" t="s">
+        <v>13</v>
       </c>
       <c r="G65" s="9"/>
     </row>
     <row r="66" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="12" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="B66" s="9" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C66" s="9" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D66" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E66" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F66" s="15" t="s">
-        <v>14</v>
+        <v>12</v>
+      </c>
+      <c r="F66" s="25" t="s">
+        <v>13</v>
       </c>
       <c r="G66" s="9"/>
     </row>
     <row r="67" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="12" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B67" s="9" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C67" s="9" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="D67" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F67" s="15" t="s">
-        <v>14</v>
+        <v>12</v>
+      </c>
+      <c r="F67" s="25" t="s">
+        <v>13</v>
       </c>
       <c r="G67" s="9"/>
     </row>
     <row r="68" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="12" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="B68" s="9" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C68" s="9" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="D68" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E68" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="F68" s="15" t="s">
-        <v>14</v>
+        <v>22</v>
+      </c>
+      <c r="F68" s="25" t="s">
+        <v>13</v>
       </c>
       <c r="G68" s="9"/>
     </row>
     <row r="69" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="12" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="B69" s="9" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C69" s="9" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D69" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F69" s="15" t="s">
-        <v>14</v>
+        <v>12</v>
+      </c>
+      <c r="F69" s="25" t="s">
+        <v>13</v>
       </c>
       <c r="G69" s="9"/>
     </row>
     <row r="70" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="12" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="B70" s="9" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C70" s="9" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D70" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E70" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F70" s="15" t="s">
-        <v>14</v>
+        <v>12</v>
+      </c>
+      <c r="F70" s="25" t="s">
+        <v>13</v>
       </c>
       <c r="G70" s="9"/>
     </row>
     <row r="71" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="12" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="B71" s="9" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C71" s="9" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D71" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="F71" s="15" t="s">
-        <v>14</v>
+        <v>22</v>
+      </c>
+      <c r="F71" s="25" t="s">
+        <v>13</v>
       </c>
       <c r="G71" s="9"/>
     </row>
     <row r="72" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="12" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="B72" s="9" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C72" s="9" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="D72" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E72" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F72" s="15" t="s">
-        <v>14</v>
+        <v>12</v>
+      </c>
+      <c r="F72" s="25" t="s">
+        <v>13</v>
       </c>
       <c r="G72" s="9"/>
     </row>
     <row r="73" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="12" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B73" s="9" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C73" s="9" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="D73" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="F73" s="15" t="s">
-        <v>14</v>
+        <v>22</v>
+      </c>
+      <c r="F73" s="25" t="s">
+        <v>13</v>
       </c>
       <c r="G73" s="9"/>
     </row>
     <row r="74" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="12" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B74" s="9" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C74" s="9" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="D74" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E74" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F74" s="15" t="s">
-        <v>14</v>
+        <v>12</v>
+      </c>
+      <c r="F74" s="25" t="s">
+        <v>13</v>
       </c>
       <c r="G74" s="9"/>
     </row>
     <row r="75" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="12" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="B75" s="9" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="C75" s="9" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="D75" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="F75" s="15" t="s">
-        <v>14</v>
+        <v>22</v>
+      </c>
+      <c r="F75" s="25" t="s">
+        <v>13</v>
       </c>
       <c r="G75" s="9"/>
     </row>
     <row r="76" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="12" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B76" s="9" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="C76" s="9" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D76" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E76" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="F76" s="15" t="s">
-        <v>14</v>
+        <v>22</v>
+      </c>
+      <c r="F76" s="25" t="s">
+        <v>13</v>
       </c>
       <c r="G76" s="9"/>
     </row>
     <row r="77" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="12" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="B77" s="9" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="C77" s="9" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="D77" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="F77" s="15" t="s">
-        <v>14</v>
+        <v>22</v>
+      </c>
+      <c r="F77" s="25" t="s">
+        <v>13</v>
       </c>
       <c r="G77" s="9"/>
     </row>
     <row r="78" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="12" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="B78" s="9" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="C78" s="9" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="D78" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E78" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="F78" s="15" t="s">
-        <v>14</v>
+        <v>56</v>
+      </c>
+      <c r="F78" s="25" t="s">
+        <v>13</v>
       </c>
       <c r="G78" s="9"/>
     </row>
     <row r="79" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="12" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B79" s="9" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C79" s="9" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="D79" s="9" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F79" s="15" t="s">
-        <v>14</v>
+        <v>12</v>
+      </c>
+      <c r="F79" s="25" t="s">
+        <v>13</v>
       </c>
       <c r="G79" s="9"/>
     </row>
     <row r="80" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="12" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="B80" s="9" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C80" s="9" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="D80" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E80" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F80" s="15" t="s">
-        <v>14</v>
+        <v>12</v>
+      </c>
+      <c r="F80" s="25" t="s">
+        <v>13</v>
       </c>
       <c r="G80" s="9"/>
     </row>
     <row r="81" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="13" t="s">
+        <v>184</v>
+      </c>
+      <c r="B81" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="C81" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="D81" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="E81" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="F81" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="G81" s="10"/>
+    </row>
+    <row r="82" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="15" t="s">
+        <v>187</v>
+      </c>
+      <c r="B82" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="C82" s="14" t="s">
         <v>188</v>
       </c>
-      <c r="B81" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="C81" s="10" t="s">
+      <c r="D82" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E82" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F82" s="25" t="s">
         <v>189</v>
       </c>
-      <c r="D81" s="10" t="s">
+      <c r="G82" s="14" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="15" t="s">
         <v>190</v>
       </c>
-      <c r="E81" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="F81" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="G81" s="10"/>
-    </row>
-    <row r="82" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="18" t="s">
+      <c r="B83" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="C83" s="14" t="s">
         <v>191</v>
       </c>
-      <c r="B82" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="C82" s="17" t="s">
+      <c r="D83" s="14" t="s">
         <v>192</v>
       </c>
-      <c r="D82" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="E82" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="F82" s="19" t="s">
+      <c r="E83" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="F83" s="25" t="s">
+        <v>189</v>
+      </c>
+      <c r="G83" s="14" t="s">
         <v>193</v>
       </c>
-      <c r="G82" s="17" t="s">
+    </row>
+    <row r="84" spans="1:7" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="26" t="s">
+        <v>242</v>
+      </c>
+      <c r="B84" s="26"/>
+      <c r="C84" s="26"/>
+      <c r="D84" s="26"/>
+      <c r="E84" s="26"/>
+      <c r="F84" s="26"/>
+      <c r="G84" s="26"/>
+    </row>
+    <row r="85" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="B85" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="C85" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="D85" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="E85" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="F85" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="G85" s="18" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="19" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="83" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="18" t="s">
+      <c r="B86" s="20" t="s">
         <v>195</v>
       </c>
-      <c r="B83" s="17" t="s">
-        <v>119</v>
-      </c>
-      <c r="C83" s="17" t="s">
+      <c r="C86" s="20" t="s">
         <v>196</v>
       </c>
-      <c r="D83" s="17" t="s">
+      <c r="D86" s="20" t="s">
         <v>197</v>
       </c>
-      <c r="E83" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="F83" s="19" t="s">
-        <v>193</v>
-      </c>
-      <c r="G83" s="17" t="s">
+      <c r="E86" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="F86" s="23" t="s">
+        <v>189</v>
+      </c>
+      <c r="G86" s="20" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="21" t="s">
         <v>198</v>
       </c>
+      <c r="B87" s="22" t="s">
+        <v>195</v>
+      </c>
+      <c r="C87" s="22" t="s">
+        <v>199</v>
+      </c>
+      <c r="D87" s="22" t="s">
+        <v>197</v>
+      </c>
+      <c r="E87" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="F87" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="G87" s="22"/>
+    </row>
+    <row r="88" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="19" t="s">
+        <v>200</v>
+      </c>
+      <c r="B88" s="20" t="s">
+        <v>195</v>
+      </c>
+      <c r="C88" s="20" t="s">
+        <v>201</v>
+      </c>
+      <c r="D88" s="20" t="s">
+        <v>197</v>
+      </c>
+      <c r="E88" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="F88" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="G88" s="20"/>
+    </row>
+    <row r="89" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="21" t="s">
+        <v>202</v>
+      </c>
+      <c r="B89" s="22" t="s">
+        <v>203</v>
+      </c>
+      <c r="C89" s="22" t="s">
+        <v>204</v>
+      </c>
+      <c r="D89" s="22" t="s">
+        <v>205</v>
+      </c>
+      <c r="E89" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="F89" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="G89" s="22"/>
+    </row>
+    <row r="90" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="19" t="s">
+        <v>206</v>
+      </c>
+      <c r="B90" s="20" t="s">
+        <v>203</v>
+      </c>
+      <c r="C90" s="20" t="s">
+        <v>243</v>
+      </c>
+      <c r="D90" s="20" t="s">
+        <v>205</v>
+      </c>
+      <c r="E90" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F90" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="G90" s="20"/>
+    </row>
+    <row r="91" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="21" t="s">
+        <v>207</v>
+      </c>
+      <c r="B91" s="22" t="s">
+        <v>203</v>
+      </c>
+      <c r="C91" s="22" t="s">
+        <v>244</v>
+      </c>
+      <c r="D91" s="22" t="s">
+        <v>205</v>
+      </c>
+      <c r="E91" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="F91" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="G91" s="22"/>
+    </row>
+    <row r="92" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="B92" s="20" t="s">
+        <v>209</v>
+      </c>
+      <c r="C92" s="20" t="s">
+        <v>210</v>
+      </c>
+      <c r="D92" s="20" t="s">
+        <v>211</v>
+      </c>
+      <c r="E92" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="F92" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="G92" s="20"/>
+    </row>
+    <row r="93" spans="1:7" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="21" t="s">
+        <v>212</v>
+      </c>
+      <c r="B93" s="22" t="s">
+        <v>209</v>
+      </c>
+      <c r="C93" s="22" t="s">
+        <v>213</v>
+      </c>
+      <c r="D93" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="E93" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="F93" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="G93" s="22"/>
+    </row>
+    <row r="94" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="19" t="s">
+        <v>214</v>
+      </c>
+      <c r="B94" s="20" t="s">
+        <v>215</v>
+      </c>
+      <c r="C94" s="20" t="s">
+        <v>216</v>
+      </c>
+      <c r="D94" s="20" t="s">
+        <v>217</v>
+      </c>
+      <c r="E94" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F94" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="G94" s="20"/>
+    </row>
+    <row r="95" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="21" t="s">
+        <v>218</v>
+      </c>
+      <c r="B95" s="22" t="s">
+        <v>215</v>
+      </c>
+      <c r="C95" s="22" t="s">
+        <v>219</v>
+      </c>
+      <c r="D95" s="22" t="s">
+        <v>217</v>
+      </c>
+      <c r="E95" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="F95" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="G95" s="22"/>
+    </row>
+    <row r="96" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="19" t="s">
+        <v>220</v>
+      </c>
+      <c r="B96" s="20" t="s">
+        <v>215</v>
+      </c>
+      <c r="C96" s="20" t="s">
+        <v>221</v>
+      </c>
+      <c r="D96" s="20" t="s">
+        <v>205</v>
+      </c>
+      <c r="E96" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="F96" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="G96" s="20"/>
+    </row>
+    <row r="97" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="21" t="s">
+        <v>222</v>
+      </c>
+      <c r="B97" s="22" t="s">
+        <v>223</v>
+      </c>
+      <c r="C97" s="22" t="s">
+        <v>224</v>
+      </c>
+      <c r="D97" s="22" t="s">
+        <v>225</v>
+      </c>
+      <c r="E97" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="F97" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="G97" s="22"/>
+    </row>
+    <row r="98" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="19" t="s">
+        <v>226</v>
+      </c>
+      <c r="B98" s="20" t="s">
+        <v>227</v>
+      </c>
+      <c r="C98" s="20" t="s">
+        <v>228</v>
+      </c>
+      <c r="D98" s="20" t="s">
+        <v>229</v>
+      </c>
+      <c r="E98" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F98" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="G98" s="20"/>
+    </row>
+    <row r="99" spans="1:7" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="21" t="s">
+        <v>230</v>
+      </c>
+      <c r="B99" s="22" t="s">
+        <v>227</v>
+      </c>
+      <c r="C99" s="22" t="s">
+        <v>231</v>
+      </c>
+      <c r="D99" s="22" t="s">
+        <v>229</v>
+      </c>
+      <c r="E99" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="F99" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="G99" s="22"/>
+    </row>
+    <row r="100" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="19" t="s">
+        <v>232</v>
+      </c>
+      <c r="B100" s="20" t="s">
+        <v>227</v>
+      </c>
+      <c r="C100" s="20" t="s">
+        <v>233</v>
+      </c>
+      <c r="D100" s="20" t="s">
+        <v>229</v>
+      </c>
+      <c r="E100" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F100" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="G100" s="20"/>
+    </row>
+    <row r="101" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="21" t="s">
+        <v>234</v>
+      </c>
+      <c r="B101" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="C101" s="22" t="s">
+        <v>236</v>
+      </c>
+      <c r="D101" s="22" t="s">
+        <v>229</v>
+      </c>
+      <c r="E101" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="F101" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="G101" s="22"/>
+    </row>
+    <row r="102" spans="1:7" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="19" t="s">
+        <v>237</v>
+      </c>
+      <c r="B102" s="20" t="s">
+        <v>235</v>
+      </c>
+      <c r="C102" s="20" t="s">
+        <v>238</v>
+      </c>
+      <c r="D102" s="20" t="s">
+        <v>229</v>
+      </c>
+      <c r="E102" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F102" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="G102" s="20"/>
+    </row>
+    <row r="103" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="21" t="s">
+        <v>239</v>
+      </c>
+      <c r="B103" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="C103" s="22" t="s">
+        <v>240</v>
+      </c>
+      <c r="D103" s="22" t="s">
+        <v>229</v>
+      </c>
+      <c r="E103" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="F103" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="G103" s="22"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="F6:F81">
-    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="Пройден"/>
-    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="Не пройден"/>
-    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="Заблокирован"/>
+  <mergeCells count="1">
+    <mergeCell ref="A84:G84"/>
+  </mergeCells>
+  <conditionalFormatting sqref="F86:F103">
+    <cfRule type="cellIs" dxfId="11" priority="25" operator="equal">
+      <formula>"Пройден"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="10" priority="26" operator="equal">
+      <formula>"Не пройден"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="9" priority="27" operator="equal">
+      <formula>"Заблокирован"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="8" priority="28" operator="equal">
+      <formula>"Не выполнен"</formula>
+    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F82:F83">
-    <cfRule type="containsText" dxfId="0" priority="4" operator="containsText" text="Не пройден"/>
+  <conditionalFormatting sqref="F6:F40">
+    <cfRule type="cellIs" dxfId="7" priority="17" operator="equal">
+      <formula>"Пройден"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="18" operator="equal">
+      <formula>"Не пройден"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="5" priority="19" operator="equal">
+      <formula>"Заблокирован"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="20" operator="equal">
+      <formula>"Не выполнен"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F41:F83">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+      <formula>"Пройден"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+      <formula>"Не пройден"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+      <formula>"Заблокирован"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
+      <formula>"Не выполнен"</formula>
+    </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="F6:F83" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" sqref="F86:F103 F6:F83" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Не выполнен,Пройден,Не пройден,Заблокирован"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>